--- a/london-youth-summer-skills-grants/budget-template.xlsx
+++ b/london-youth-summer-skills-grants/budget-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29728"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BeverleyAnim-Antwi\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://londonyouth1.sharepoint.com/Shared Documents/Delivery/Employabilty/CVC Summer Grants/2023/Application Process/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A33EDE-631F-4ED4-BF08-A24B324C2A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{6474CC19-28F8-4BD9-8786-A3F155590C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A68ADA94-E376-49CC-8191-CAF1615C2B95}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
   <si>
-    <t>Summer Skills Grants 2025</t>
+    <t>Summer Skills Grants 2026</t>
   </si>
   <si>
     <t>Budget Template</t>
@@ -103,6 +103,9 @@
     <t>[  ]</t>
   </si>
   <si>
+    <t>Proposed Project:</t>
+  </si>
+  <si>
     <t>Start and end dates:</t>
   </si>
   <si>
@@ -185,9 +188,6 @@
   </si>
   <si>
     <t>If TRUE then funding = expenditure</t>
-  </si>
-  <si>
-    <t>Proposed Project:</t>
   </si>
 </sst>
 </file>
@@ -198,7 +198,7 @@
     <numFmt numFmtId="164" formatCode="0%_);\(0%\);&quot;–&quot;_)"/>
     <numFmt numFmtId="165" formatCode="#,##0_);\(#,##0\);\–_);&quot;–&quot;_)"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -573,21 +573,21 @@
   <dxfs count="2">
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -969,29 +969,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C2:Q39"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="1.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="45.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="61.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="45.1796875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="11.26953125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.1796875" style="1"/>
+    <col min="1" max="2" width="1.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="45.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="61.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.140625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="11.28515625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:17" ht="32.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="3:17" ht="33.75">
       <c r="C2" s="35" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="35"/>
     </row>
-    <row r="3" spans="3:17" ht="27.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:17" ht="27">
       <c r="C3" s="9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="3:17" s="3" customFormat="1" ht="5.15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="3:17" s="3" customFormat="1" ht="5.0999999999999996" customHeight="1"/>
+    <row r="6" spans="3:17" ht="15.75">
       <c r="C6" s="4" t="s">
         <v>2</v>
       </c>
@@ -999,25 +999,25 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:17" ht="15.75">
       <c r="C7" s="5" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="3:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:17" ht="15.75">
       <c r="C8" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="3:17" ht="20" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:17" ht="20.25">
       <c r="C10" s="17" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
@@ -1025,7 +1025,7 @@
       <c r="G10" s="14"/>
       <c r="H10" s="30"/>
       <c r="I10" s="31" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J10" s="32"/>
       <c r="K10" s="32"/>
@@ -1036,25 +1036,25 @@
       <c r="P10" s="32"/>
       <c r="Q10" s="33"/>
     </row>
-    <row r="12" spans="3:17" ht="18" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:17" ht="18">
       <c r="C12" s="19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J12" s="19"/>
       <c r="K12" s="19"/>
@@ -1064,15 +1064,15 @@
       <c r="O12" s="19"/>
       <c r="P12" s="19"/>
     </row>
-    <row r="13" spans="3:17" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:17" ht="18">
       <c r="C13" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13" s="26">
         <f>15*50</f>
@@ -1093,10 +1093,10 @@
       <c r="P13" s="36"/>
       <c r="Q13" s="36"/>
     </row>
-    <row r="14" spans="3:17" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:17" ht="18">
       <c r="C14" s="8"/>
       <c r="D14" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="26"/>
@@ -1115,10 +1115,10 @@
       <c r="P14" s="36"/>
       <c r="Q14" s="36"/>
     </row>
-    <row r="15" spans="3:17" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:17" ht="18">
       <c r="C15" s="8"/>
       <c r="D15" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="26">
@@ -1139,10 +1139,10 @@
       <c r="P15" s="36"/>
       <c r="Q15" s="36"/>
     </row>
-    <row r="16" spans="3:17" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:17" ht="18">
       <c r="C16" s="8"/>
       <c r="D16" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="26">
@@ -1163,7 +1163,7 @@
       <c r="P16" s="36"/>
       <c r="Q16" s="36"/>
     </row>
-    <row r="17" spans="3:17" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:17" ht="18">
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
@@ -1185,7 +1185,7 @@
       <c r="P17" s="36"/>
       <c r="Q17" s="36"/>
     </row>
-    <row r="18" spans="3:17" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:17" ht="18">
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
@@ -1207,7 +1207,7 @@
       <c r="P18" s="36"/>
       <c r="Q18" s="36"/>
     </row>
-    <row r="19" spans="3:17" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:17" ht="18">
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
@@ -1229,7 +1229,7 @@
       <c r="P19" s="36"/>
       <c r="Q19" s="36"/>
     </row>
-    <row r="20" spans="3:17" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:17" ht="18">
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
@@ -1251,7 +1251,7 @@
       <c r="P20" s="36"/>
       <c r="Q20" s="36"/>
     </row>
-    <row r="21" spans="3:17" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:17" ht="18">
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -1273,7 +1273,7 @@
       <c r="P21" s="36"/>
       <c r="Q21" s="36"/>
     </row>
-    <row r="22" spans="3:17" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:17" ht="18">
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -1295,7 +1295,7 @@
       <c r="P22" s="36"/>
       <c r="Q22" s="36"/>
     </row>
-    <row r="23" spans="3:17" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:17" ht="18">
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
@@ -1317,7 +1317,7 @@
       <c r="P23" s="36"/>
       <c r="Q23" s="36"/>
     </row>
-    <row r="24" spans="3:17" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:17" ht="18">
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
@@ -1339,7 +1339,7 @@
       <c r="P24" s="36"/>
       <c r="Q24" s="36"/>
     </row>
-    <row r="25" spans="3:17" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:17" ht="18">
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
@@ -1361,9 +1361,9 @@
       <c r="P25" s="36"/>
       <c r="Q25" s="36"/>
     </row>
-    <row r="26" spans="3:17" ht="18" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:17" ht="18">
       <c r="C26" s="22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D26" s="23"/>
       <c r="E26" s="23"/>
@@ -1385,7 +1385,7 @@
       <c r="O26" s="8"/>
       <c r="P26" s="8"/>
     </row>
-    <row r="27" spans="3:17" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:17" ht="18">
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
@@ -1401,16 +1401,16 @@
       <c r="O27" s="8"/>
       <c r="P27" s="8"/>
     </row>
-    <row r="30" spans="3:17" ht="20" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:17" ht="20.25">
       <c r="C30" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D30" s="15"/>
       <c r="E30" s="15"/>
       <c r="F30" s="15"/>
       <c r="G30" s="16"/>
       <c r="I30" s="31" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J30" s="32"/>
       <c r="K30" s="32"/>
@@ -1421,25 +1421,25 @@
       <c r="P30" s="32"/>
       <c r="Q30" s="33"/>
     </row>
-    <row r="32" spans="3:17" ht="18" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:17" ht="18">
       <c r="C32" s="19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H32" s="8"/>
       <c r="I32" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J32" s="19"/>
       <c r="K32" s="19"/>
@@ -1449,12 +1449,12 @@
       <c r="O32" s="19"/>
       <c r="P32" s="19"/>
     </row>
-    <row r="33" spans="3:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:16" ht="18">
       <c r="C33" s="34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>3</v>
@@ -1476,12 +1476,12 @@
       <c r="O33" s="8"/>
       <c r="P33" s="8"/>
     </row>
-    <row r="34" spans="3:16" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:16" ht="18">
       <c r="C34" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>3</v>
@@ -1503,12 +1503,12 @@
       <c r="O34" s="8"/>
       <c r="P34" s="8"/>
     </row>
-    <row r="35" spans="3:16" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:16" ht="18">
       <c r="C35" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>3</v>
@@ -1530,12 +1530,12 @@
       <c r="O35" s="8"/>
       <c r="P35" s="8"/>
     </row>
-    <row r="36" spans="3:16" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:16" ht="18">
       <c r="C36" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>3</v>
@@ -1557,9 +1557,9 @@
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
     </row>
-    <row r="37" spans="3:16" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:16" s="2" customFormat="1" ht="18">
       <c r="C37" s="22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D37" s="22"/>
       <c r="E37" s="22"/>
@@ -1581,7 +1581,7 @@
       <c r="O37" s="7"/>
       <c r="P37" s="7"/>
     </row>
-    <row r="38" spans="3:16" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:16" ht="18">
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
@@ -1597,12 +1597,12 @@
       <c r="O38" s="8"/>
       <c r="P38" s="8"/>
     </row>
-    <row r="39" spans="3:16" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:16" ht="18.75">
       <c r="C39" s="27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E39" s="28"/>
       <c r="F39" s="28" t="b">
@@ -1626,11 +1626,11 @@
     <mergeCell ref="I13:Q25"/>
   </mergeCells>
   <conditionalFormatting sqref="F39">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>TRUE</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>FALSE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1641,8 +1641,93 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010036CF3F84F056D74D818EB65583F210CD" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9185b25e12de13791a94f4023c2bd296">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3795fb6b-72da-42bf-89c2-2c41d718d404" xmlns:ns3="f960e734-b488-49a0-bcdc-279f0dff28e5" xmlns:ns4="http://schemas.microsoft.com/sharepoint/v4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="32d42beeece16d94a818512d2f57b34a" ns2:_="" ns3:_="" ns4:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <IconOverlay xmlns="http://schemas.microsoft.com/sharepoint/v4" xsi:nil="true"/>
+    <_dlc_DocId xmlns="f960e734-b488-49a0-bcdc-279f0dff28e5">CEX5WWDRJUFA-2102554853-1167544</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="f960e734-b488-49a0-bcdc-279f0dff28e5">
+      <Url>https://londonyouth1.sharepoint.com/_layouts/15/DocIdRedir.aspx?ID=CEX5WWDRJUFA-2102554853-1167544</Url>
+      <Description>CEX5WWDRJUFA-2102554853-1167544</Description>
+    </_dlc_DocIdUrl>
+    <SharedWithUsers xmlns="f960e734-b488-49a0-bcdc-279f0dff28e5">
+      <UserInfo>
+        <DisplayName>Kelly Dummer</DisplayName>
+        <AccountId>3323</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <MediaLengthInSeconds xmlns="3795fb6b-72da-42bf-89c2-2c41d718d404" xsi:nil="true"/>
+    <_dlc_DocIdPersistId xmlns="f960e734-b488-49a0-bcdc-279f0dff28e5">false</_dlc_DocIdPersistId>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3795fb6b-72da-42bf-89c2-2c41d718d404">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f960e734-b488-49a0-bcdc-279f0dff28e5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010036CF3F84F056D74D818EB65583F210CD" ma:contentTypeVersion="23" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="36b8b17401ce8d662818173f6cd3626c">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3795fb6b-72da-42bf-89c2-2c41d718d404" xmlns:ns3="f960e734-b488-49a0-bcdc-279f0dff28e5" xmlns:ns4="http://schemas.microsoft.com/sharepoint/v4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="987f6fa7aafe98daaf403cd6b61af8ae" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3795fb6b-72da-42bf-89c2-2c41d718d404"/>
     <xsd:import namespace="f960e734-b488-49a0-bcdc-279f0dff28e5"/>
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v4"/>
@@ -1673,6 +1758,7 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1755,6 +1841,11 @@
       </xsd:simpleType>
     </xsd:element>
     <xsd:element name="MediaServiceSearchProperties" ma:index="29" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="30" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
@@ -1931,135 +2022,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <IconOverlay xmlns="http://schemas.microsoft.com/sharepoint/v4" xsi:nil="true"/>
-    <_dlc_DocId xmlns="f960e734-b488-49a0-bcdc-279f0dff28e5">CEX5WWDRJUFA-2102554853-1091328</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="f960e734-b488-49a0-bcdc-279f0dff28e5">
-      <Url>https://londonyouth1.sharepoint.com/_layouts/15/DocIdRedir.aspx?ID=CEX5WWDRJUFA-2102554853-1091328</Url>
-      <Description>CEX5WWDRJUFA-2102554853-1091328</Description>
-    </_dlc_DocIdUrl>
-    <SharedWithUsers xmlns="f960e734-b488-49a0-bcdc-279f0dff28e5">
-      <UserInfo>
-        <DisplayName>Kelly Dummer</DisplayName>
-        <AccountId>3323</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <MediaLengthInSeconds xmlns="3795fb6b-72da-42bf-89c2-2c41d718d404" xsi:nil="true"/>
-    <_dlc_DocIdPersistId xmlns="f960e734-b488-49a0-bcdc-279f0dff28e5">false</_dlc_DocIdPersistId>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3795fb6b-72da-42bf-89c2-2c41d718d404">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f960e734-b488-49a0-bcdc-279f0dff28e5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4E7E186-C437-4D7E-87FC-F2995D2E0203}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3795fb6b-72da-42bf-89c2-2c41d718d404"/>
-    <ds:schemaRef ds:uri="f960e734-b488-49a0-bcdc-279f0dff28e5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FA3912E-6748-410F-8217-41DFB623FC67}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1591D37-0CF1-4A8D-88B0-0EE94E14EB66}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E56A476-5E5A-4446-9731-6CCEEE1697B0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E56A476-5E5A-4446-9731-6CCEEE1697B0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
-    <ds:schemaRef ds:uri="f960e734-b488-49a0-bcdc-279f0dff28e5"/>
-    <ds:schemaRef ds:uri="3795fb6b-72da-42bf-89c2-2c41d718d404"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1591D37-0CF1-4A8D-88B0-0EE94E14EB66}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FA3912E-6748-410F-8217-41DFB623FC67}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C67DFAFE-CD4E-4923-AA05-E33DF56E4816}"/>
 </file>